--- a/Lab-trails/2026-04-14-Density-exp/2026-04-14-density-exp-Soil.xlsx
+++ b/Lab-trails/2026-04-14-Density-exp/2026-04-14-density-exp-Soil.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mikae\Desktop\Github - speciale\Larsen-2025-Masterthesis-DFCs\Lab-trails\2026-04-14-Density-exp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CD59B82-3C78-491E-B68C-BB443425372B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{955B0A27-BB2E-4FD9-B5E3-95B9DE74F85E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="360" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ark1" sheetId="1" r:id="rId1"/>
@@ -35,8 +35,35 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>tc={E6C46A10-5F23-4C63-B09B-4044A09A68A5}</author>
+    <author>tc={4E536A07-532F-45D7-94C5-941ACF3C7F7D}</author>
+  </authors>
+  <commentList>
+    <comment ref="B2" authorId="0" shapeId="0" xr:uid="{E6C46A10-5F23-4C63-B09B-4044A09A68A5}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    The week before starting the experiment</t>
+      </text>
+    </comment>
+    <comment ref="B8" authorId="1" shapeId="0" xr:uid="{4E536A07-532F-45D7-94C5-941ACF3C7F7D}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Just after packing the soils</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="33">
   <si>
     <t>ID</t>
   </si>
@@ -132,16 +159,20 @@
   </si>
   <si>
     <t>n(stamps)</t>
+  </si>
+  <si>
+    <t>Date</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.000"/>
+    <numFmt numFmtId="167" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -156,6 +187,12 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="4">
@@ -197,8 +234,8 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="2" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -214,6 +251,12 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <person displayName="Mikael Løvig Larsen" id="{09E67358-F804-4B97-832D-8600B841E772}" userId="S::au705323@uni.au.dk::501b5c6e-34b9-41fc-bcf2-dc0650cde639" providerId="AD"/>
+</personList>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -477,16 +520,30 @@
 </a:theme>
 </file>
 
+<file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="B2" dT="2026-04-15T09:57:10.83" personId="{09E67358-F804-4B97-832D-8600B841E772}" id="{E6C46A10-5F23-4C63-B09B-4044A09A68A5}">
+    <text>The week before starting the experiment</text>
+  </threadedComment>
+  <threadedComment ref="B8" dT="2026-04-15T09:58:38.45" personId="{09E67358-F804-4B97-832D-8600B841E772}" id="{4E536A07-532F-45D7-94C5-941ACF3C7F7D}">
+    <text>Just after packing the soils</text>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:X7"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:Y10"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="14.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.5546875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.21875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="11.109375" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="27.5546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="28.88671875" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="17.21875" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="21.44140625" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="27.5546875" bestFit="1" customWidth="1"/>
@@ -502,368 +559,480 @@
     <col min="23" max="23" width="14.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>11</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>10</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>12</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>13</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>17</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>18</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>0</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>20</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>19</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>24</v>
       </c>
-      <c r="P1" s="6" t="s">
+      <c r="Q1" t="s">
         <v>25</v>
       </c>
-      <c r="Q1" s="6" t="s">
+      <c r="R1" t="s">
         <v>26</v>
       </c>
-      <c r="R1" s="6" t="s">
+      <c r="S1" t="s">
         <v>28</v>
       </c>
-      <c r="S1" s="6" t="s">
+      <c r="T1" t="s">
         <v>29</v>
       </c>
-      <c r="T1" s="6" t="s">
+      <c r="U1" t="s">
         <v>30</v>
       </c>
-      <c r="U1" s="6" t="s">
+      <c r="V1" t="s">
         <v>27</v>
       </c>
-      <c r="W1" s="4" t="s">
+      <c r="X1" s="4" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="1">
+      <c r="B2" s="6">
+        <v>46121</v>
+      </c>
+      <c r="C2" s="1">
         <v>125.25</v>
       </c>
-      <c r="C2">
+      <c r="D2">
         <v>4.2910000000000004</v>
       </c>
-      <c r="D2" s="1">
-        <f>B2-C2</f>
+      <c r="E2" s="1">
+        <f>C2-D2</f>
         <v>120.959</v>
       </c>
-      <c r="E2">
+      <c r="F2">
         <v>100.849</v>
       </c>
-      <c r="F2">
-        <f>E2-C2</f>
+      <c r="G2">
+        <f>F2-D2</f>
         <v>96.558000000000007</v>
       </c>
-      <c r="G2" s="1">
-        <f>D2-F2</f>
+      <c r="H2" s="1">
+        <f>E2-G2</f>
         <v>24.400999999999996</v>
       </c>
-      <c r="H2" s="2">
-        <f>G2/F2</f>
+      <c r="I2" s="2">
+        <f>H2/G2</f>
         <v>0.25270821682304928</v>
       </c>
-      <c r="I2" s="2">
-        <f>AVERAGE(H2:H4)</f>
+      <c r="J2" s="2">
+        <f>AVERAGE(I2:I4)</f>
         <v>0.2518198659885334</v>
       </c>
-      <c r="J2" s="2">
-        <f>_xlfn.STDEV.P(H2:H4)</f>
+      <c r="K2" s="2">
+        <f>_xlfn.STDEV.P(I2:I4)</f>
         <v>9.0608450540909605E-3</v>
       </c>
-      <c r="L2" t="s">
+      <c r="M2" t="s">
         <v>14</v>
       </c>
-      <c r="M2" s="2">
+      <c r="N2" s="2">
         <v>1.5</v>
       </c>
-      <c r="N2" s="2">
+      <c r="O2" s="2">
         <v>0.25</v>
       </c>
-      <c r="O2" s="3"/>
       <c r="P2" s="3"/>
       <c r="Q2" s="3"/>
       <c r="R2" s="3"/>
       <c r="S2" s="3"/>
       <c r="T2" s="3"/>
       <c r="U2" s="3"/>
-      <c r="W2" t="s">
+      <c r="V2" s="3"/>
+      <c r="X2" t="s">
         <v>21</v>
       </c>
-      <c r="X2">
+      <c r="Y2">
         <v>100</v>
       </c>
     </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="1">
+      <c r="B3" s="6">
+        <v>46121</v>
+      </c>
+      <c r="C3" s="1">
         <v>138.08099999999999</v>
       </c>
-      <c r="C3">
+      <c r="D3">
         <v>4.2919999999999998</v>
       </c>
-      <c r="D3" s="1">
-        <f t="shared" ref="D3:D7" si="0">B3-C3</f>
+      <c r="E3" s="1">
+        <f t="shared" ref="E3:E10" si="0">C3-D3</f>
         <v>133.78899999999999</v>
       </c>
-      <c r="E3">
+      <c r="F3">
         <v>110.268</v>
       </c>
-      <c r="F3">
-        <f t="shared" ref="F3:F7" si="1">E3-C3</f>
+      <c r="G3">
+        <f t="shared" ref="G3:G10" si="1">F3-D3</f>
         <v>105.976</v>
       </c>
-      <c r="G3" s="1">
-        <f t="shared" ref="G3:G7" si="2">D3-F3</f>
+      <c r="H3" s="1">
+        <f t="shared" ref="H3:H10" si="2">E3-G3</f>
         <v>27.812999999999988</v>
       </c>
-      <c r="H3" s="2">
-        <f t="shared" ref="H3:H7" si="3">G3/F3</f>
+      <c r="I3" s="2">
+        <f t="shared" ref="I3:I10" si="3">H3/G3</f>
         <v>0.26244621423718567</v>
       </c>
-      <c r="L3" t="s">
+      <c r="M3" t="s">
         <v>15</v>
       </c>
-      <c r="M3" s="2">
+      <c r="N3" s="2">
         <v>1.5</v>
       </c>
-      <c r="N3" s="2" t="s">
+      <c r="O3" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="O3" s="2">
+      <c r="P3" s="2">
         <v>150</v>
       </c>
-      <c r="P3" s="7">
-        <f>O3*I5</f>
+      <c r="Q3" s="2">
+        <f>P3*J5</f>
         <v>26.294748691286532</v>
       </c>
-      <c r="Q3" s="7">
-        <f>O3+P3</f>
+      <c r="R3" s="2">
+        <f>P3+Q3</f>
         <v>176.29474869128654</v>
       </c>
-      <c r="R3" s="5">
-        <f>Q3/4</f>
+      <c r="S3" s="5">
+        <f>R3/4</f>
         <v>44.073687172821636</v>
       </c>
-      <c r="S3" s="2">
-        <f>O3*I2</f>
+      <c r="T3" s="2">
+        <f>P3*J2</f>
         <v>37.772979898280006</v>
       </c>
-      <c r="T3" s="2">
-        <f>S3-P3</f>
+      <c r="U3" s="2">
+        <f>T3-Q3</f>
         <v>11.478231206993474</v>
       </c>
-      <c r="U3" s="5">
-        <f>T3/X3</f>
+      <c r="V3" s="5">
+        <f>U3/Y3</f>
         <v>2.8695578017483685</v>
       </c>
-      <c r="W3" t="s">
+      <c r="X3" t="s">
         <v>31</v>
       </c>
-      <c r="X3">
+      <c r="Y3">
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="1">
+      <c r="B4" s="6">
+        <v>46121</v>
+      </c>
+      <c r="C4" s="1">
         <v>94.373000000000005</v>
       </c>
-      <c r="C4">
+      <c r="D4">
         <v>4.3070000000000004</v>
       </c>
-      <c r="D4" s="1">
+      <c r="E4" s="1">
         <f t="shared" si="0"/>
         <v>90.066000000000003</v>
       </c>
-      <c r="E4">
+      <c r="F4">
         <v>76.923000000000002</v>
       </c>
-      <c r="F4">
+      <c r="G4">
         <f t="shared" si="1"/>
         <v>72.616</v>
       </c>
-      <c r="G4" s="1">
+      <c r="H4" s="1">
         <f t="shared" si="2"/>
         <v>17.450000000000003</v>
       </c>
-      <c r="H4" s="2">
+      <c r="I4" s="2">
         <f t="shared" si="3"/>
         <v>0.24030516690536524</v>
       </c>
-      <c r="L4" t="s">
+      <c r="M4" t="s">
         <v>16</v>
       </c>
-      <c r="M4" s="5">
+      <c r="N4" s="5">
         <v>1.2</v>
       </c>
-      <c r="N4" t="s">
+      <c r="O4" t="s">
         <v>23</v>
       </c>
-      <c r="O4" s="2">
+      <c r="P4" s="2">
         <v>120</v>
       </c>
-      <c r="P4" s="7">
-        <f>O4*I5</f>
+      <c r="Q4" s="2">
+        <f>P4*J5</f>
         <v>21.035798953029225</v>
       </c>
-      <c r="Q4" s="7">
-        <f>O4+P4</f>
+      <c r="R4" s="2">
+        <f>P4+Q4</f>
         <v>141.03579895302923</v>
       </c>
-      <c r="R4" s="5">
-        <f>Q4/4</f>
+      <c r="S4" s="5">
+        <f>R4/4</f>
         <v>35.258949738257307</v>
       </c>
-      <c r="S4" s="2">
-        <f>O4*I2</f>
+      <c r="T4" s="2">
+        <f>P4*J2</f>
         <v>30.218383918624006</v>
       </c>
-      <c r="T4" s="2">
-        <f>S4-P4</f>
+      <c r="U4" s="2">
+        <f>T4-Q4</f>
         <v>9.1825849655947813</v>
       </c>
-      <c r="U4" s="5">
-        <f>T4/X3</f>
+      <c r="V4" s="5">
+        <f>U4/Y3</f>
         <v>2.2956462413986953</v>
       </c>
     </row>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="1">
+      <c r="B5" s="6">
+        <v>46121</v>
+      </c>
+      <c r="C5" s="1">
         <v>116.807</v>
       </c>
-      <c r="C5">
+      <c r="D5">
         <v>4.2990000000000004</v>
       </c>
-      <c r="D5" s="1">
+      <c r="E5" s="1">
         <f t="shared" si="0"/>
         <v>112.508</v>
       </c>
-      <c r="E5">
+      <c r="F5">
         <v>98.825999999999993</v>
       </c>
-      <c r="F5">
+      <c r="G5">
         <f t="shared" si="1"/>
         <v>94.526999999999987</v>
       </c>
-      <c r="G5" s="1">
+      <c r="H5" s="1">
         <f t="shared" si="2"/>
         <v>17.981000000000009</v>
       </c>
-      <c r="H5" s="2">
+      <c r="I5" s="2">
         <f t="shared" si="3"/>
         <v>0.19022078347985244</v>
       </c>
-      <c r="I5" s="2">
-        <f>AVERAGE(H5:H7)</f>
+      <c r="J5" s="2">
+        <f>AVERAGE(I5:I7)</f>
         <v>0.17529832460857689</v>
       </c>
-      <c r="J5" s="2">
-        <f>_xlfn.STDEV.P(H5:H7)</f>
+      <c r="K5" s="2">
+        <f>_xlfn.STDEV.P(I5:I7)</f>
         <v>2.0374328006409408E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="1">
+      <c r="B6" s="6">
+        <v>46121</v>
+      </c>
+      <c r="C6" s="1">
         <v>117.89100000000001</v>
       </c>
-      <c r="C6">
+      <c r="D6">
         <v>4.3070000000000004</v>
       </c>
-      <c r="D6" s="1">
+      <c r="E6" s="1">
         <f t="shared" si="0"/>
         <v>113.584</v>
       </c>
-      <c r="E6">
+      <c r="F6">
         <v>103.378</v>
       </c>
-      <c r="F6">
+      <c r="G6">
         <f t="shared" si="1"/>
         <v>99.070999999999998</v>
       </c>
-      <c r="G6" s="1">
+      <c r="H6" s="1">
         <f t="shared" si="2"/>
         <v>14.513000000000005</v>
       </c>
-      <c r="H6" s="2">
+      <c r="I6" s="2">
         <f t="shared" si="3"/>
         <v>0.1464909004653229</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="1">
+      <c r="B7" s="6">
+        <v>46121</v>
+      </c>
+      <c r="C7" s="1">
         <v>102.38</v>
       </c>
-      <c r="C7">
+      <c r="D7">
         <v>4.3140000000000001</v>
       </c>
-      <c r="D7" s="1">
+      <c r="E7" s="1">
         <f t="shared" si="0"/>
         <v>98.066000000000003</v>
       </c>
-      <c r="E7">
+      <c r="F7">
         <v>86.778999999999996</v>
       </c>
-      <c r="F7">
+      <c r="G7">
         <f t="shared" si="1"/>
         <v>82.465000000000003</v>
       </c>
-      <c r="G7" s="1">
+      <c r="H7" s="1">
         <f t="shared" si="2"/>
         <v>15.600999999999999</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <f t="shared" si="3"/>
         <v>0.18918328988055536</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" s="6">
+        <v>46125</v>
+      </c>
+      <c r="C8" s="1">
+        <v>54.576999999999998</v>
+      </c>
+      <c r="D8">
+        <v>4.3040000000000003</v>
+      </c>
+      <c r="E8" s="1">
+        <f t="shared" si="0"/>
+        <v>50.272999999999996</v>
+      </c>
+      <c r="G8">
+        <f t="shared" si="1"/>
+        <v>-4.3040000000000003</v>
+      </c>
+      <c r="H8" s="1">
+        <f t="shared" si="2"/>
+        <v>54.576999999999998</v>
+      </c>
+      <c r="I8" s="2">
+        <f t="shared" si="3"/>
+        <v>-12.680529739776951</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" s="6">
+        <v>46125</v>
+      </c>
+      <c r="C9" s="1">
+        <v>54.875999999999998</v>
+      </c>
+      <c r="D9">
+        <v>4.2949999999999999</v>
+      </c>
+      <c r="E9" s="1">
+        <f t="shared" si="0"/>
+        <v>50.580999999999996</v>
+      </c>
+      <c r="G9">
+        <f t="shared" si="1"/>
+        <v>-4.2949999999999999</v>
+      </c>
+      <c r="H9" s="1">
+        <f t="shared" si="2"/>
+        <v>54.875999999999998</v>
+      </c>
+      <c r="I9" s="2">
+        <f t="shared" si="3"/>
+        <v>-12.776717112922002</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10" s="6">
+        <v>46125</v>
+      </c>
+      <c r="C10" s="1">
+        <v>54.093000000000004</v>
+      </c>
+      <c r="D10" s="7">
+        <v>4.3</v>
+      </c>
+      <c r="E10" s="1">
+        <f t="shared" si="0"/>
+        <v>49.793000000000006</v>
+      </c>
+      <c r="G10">
+        <f t="shared" si="1"/>
+        <v>-4.3</v>
+      </c>
+      <c r="H10" s="1">
+        <f t="shared" si="2"/>
+        <v>54.093000000000004</v>
+      </c>
+      <c r="I10" s="2">
+        <f t="shared" si="3"/>
+        <v>-12.579767441860467</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/Lab-trails/2026-04-14-Density-exp/2026-04-14-density-exp-Soil.xlsx
+++ b/Lab-trails/2026-04-14-Density-exp/2026-04-14-density-exp-Soil.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mikae\Desktop\Github - speciale\Larsen-2025-Masterthesis-DFCs\Lab-trails\2026-04-14-Density-exp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{955B0A27-BB2E-4FD9-B5E3-95B9DE74F85E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0185186B-0E8C-4E74-A699-D20B11F0466D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ark1" sheetId="1" r:id="rId1"/>
@@ -170,9 +170,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.000"/>
-    <numFmt numFmtId="167" formatCode="0.0000"/>
+    <numFmt numFmtId="165" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -187,12 +187,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="4">
@@ -235,7 +229,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="2" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -958,17 +952,28 @@
         <f t="shared" si="0"/>
         <v>50.272999999999996</v>
       </c>
+      <c r="F8">
+        <v>46.543999999999997</v>
+      </c>
       <c r="G8">
         <f t="shared" si="1"/>
-        <v>-4.3040000000000003</v>
+        <v>42.239999999999995</v>
       </c>
       <c r="H8" s="1">
         <f t="shared" si="2"/>
-        <v>54.576999999999998</v>
+        <v>8.0330000000000013</v>
       </c>
       <c r="I8" s="2">
         <f t="shared" si="3"/>
-        <v>-12.680529739776951</v>
+        <v>0.19017518939393946</v>
+      </c>
+      <c r="J8" s="2">
+        <f>AVERAGE(I8:I10)</f>
+        <v>0.18908502410708605</v>
+      </c>
+      <c r="K8" s="1">
+        <f>_xlfn.STDEV.P(I8:I10)</f>
+        <v>1.1477299017479126E-3</v>
       </c>
     </row>
     <row r="9" spans="1:25" x14ac:dyDescent="0.3">
@@ -988,17 +993,20 @@
         <f t="shared" si="0"/>
         <v>50.580999999999996</v>
       </c>
+      <c r="F9">
+        <v>46.814999999999998</v>
+      </c>
       <c r="G9">
         <f t="shared" si="1"/>
-        <v>-4.2949999999999999</v>
+        <v>42.519999999999996</v>
       </c>
       <c r="H9" s="1">
         <f t="shared" si="2"/>
-        <v>54.875999999999998</v>
+        <v>8.0609999999999999</v>
       </c>
       <c r="I9" s="2">
         <f t="shared" si="3"/>
-        <v>-12.776717112922002</v>
+        <v>0.18958137347130763</v>
       </c>
     </row>
     <row r="10" spans="1:25" x14ac:dyDescent="0.3">
@@ -1018,17 +1026,20 @@
         <f t="shared" si="0"/>
         <v>49.793000000000006</v>
       </c>
+      <c r="F10">
+        <v>46.231000000000002</v>
+      </c>
       <c r="G10">
         <f t="shared" si="1"/>
-        <v>-4.3</v>
+        <v>41.931000000000004</v>
       </c>
       <c r="H10" s="1">
         <f t="shared" si="2"/>
-        <v>54.093000000000004</v>
+        <v>7.8620000000000019</v>
       </c>
       <c r="I10" s="2">
         <f t="shared" si="3"/>
-        <v>-12.579767441860467</v>
+        <v>0.1874985094560111</v>
       </c>
     </row>
   </sheetData>

--- a/Lab-trails/2026-04-14-Density-exp/2026-04-14-density-exp-Soil.xlsx
+++ b/Lab-trails/2026-04-14-Density-exp/2026-04-14-density-exp-Soil.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mikae\Desktop\Github - speciale\Larsen-2025-Masterthesis-DFCs\Lab-trails\2026-04-14-Density-exp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0185186B-0E8C-4E74-A699-D20B11F0466D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00E7963B-83C0-4E21-BB81-ACCB32F1814D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -47,7 +47,7 @@
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
-    The week before starting the experiment</t>
+    The week before starting the experiment, sived soil</t>
       </text>
     </comment>
     <comment ref="B8" authorId="1" shapeId="0" xr:uid="{4E536A07-532F-45D7-94C5-941ACF3C7F7D}">
@@ -221,7 +221,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -230,6 +230,7 @@
     <xf numFmtId="2" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -517,7 +518,7 @@
 <file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <threadedComment ref="B2" dT="2026-04-15T09:57:10.83" personId="{09E67358-F804-4B97-832D-8600B841E772}" id="{E6C46A10-5F23-4C63-B09B-4044A09A68A5}">
-    <text>The week before starting the experiment</text>
+    <text>The week before starting the experiment, sived soil</text>
   </threadedComment>
   <threadedComment ref="B8" dT="2026-04-15T09:58:38.45" personId="{09E67358-F804-4B97-832D-8600B841E772}" id="{4E536A07-532F-45D7-94C5-941ACF3C7F7D}">
     <text>Just after packing the soils</text>
@@ -543,14 +544,14 @@
     <col min="12" max="12" width="27.5546875" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="21.44140625" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="27.5546875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="17.33203125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="16.5546875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="12.21875" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="20.88671875" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="16.109375" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.77734375" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="11.77734375" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="25.88671875" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="16.5546875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="12.109375" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="20.88671875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="16.109375" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.77734375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="11.77734375" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:25" x14ac:dyDescent="0.3">
@@ -726,6 +727,7 @@
         <v>23</v>
       </c>
       <c r="P3" s="2">
+        <f>N3*Y2</f>
         <v>150</v>
       </c>
       <c r="Q3" s="2">
@@ -794,13 +796,14 @@
       <c r="M4" t="s">
         <v>16</v>
       </c>
-      <c r="N4" s="5">
+      <c r="N4" s="8">
         <v>1.2</v>
       </c>
       <c r="O4" t="s">
         <v>23</v>
       </c>
       <c r="P4" s="2">
+        <f>N4*Y2</f>
         <v>120</v>
       </c>
       <c r="Q4" s="2">

--- a/Lab-trails/2026-04-14-Density-exp/2026-04-14-density-exp-Soil.xlsx
+++ b/Lab-trails/2026-04-14-Density-exp/2026-04-14-density-exp-Soil.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mikae\Desktop\Github - speciale\Larsen-2025-Masterthesis-DFCs\Lab-trails\2026-04-14-Density-exp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00E7963B-83C0-4E21-BB81-ACCB32F1814D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15C6F002-E6DA-4FEC-8244-FBE5B7AE3640}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -221,7 +221,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -230,7 +230,6 @@
     <xf numFmtId="2" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -796,7 +795,7 @@
       <c r="M4" t="s">
         <v>16</v>
       </c>
-      <c r="N4" s="8">
+      <c r="N4" s="2">
         <v>1.2</v>
       </c>
       <c r="O4" t="s">
